--- a/Action/Data/CSV/MobEnemy1/MobEnemyData.xlsx
+++ b/Action/Data/CSV/MobEnemy1/MobEnemyData.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2409404\Desktop\GameProject\Action\Data\CSV\MobEnemy\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ita20\OneDrive\デスクトップ\GameProject\Action\Data\CSV\MobEnemy1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DFE8DC6B-2215-4E0F-8D94-F334AD5C9C89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6E1B49E1-DD48-4F8F-8F06-A3004FE0E07A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -681,9 +681,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 テーマ">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -721,7 +721,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -827,7 +827,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -969,7 +969,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -977,13 +977,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="16" width="5.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A1">
         <v>0</v>
       </c>
@@ -1023,8 +1023,11 @@
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M1">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>0</v>
       </c>
@@ -1064,8 +1067,11 @@
         <f t="shared" ref="L2:L25" si="3">I2*20</f>
         <v>20</v>
       </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M2">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>50</v>
       </c>
@@ -1105,8 +1111,11 @@
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M3">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>-50</v>
       </c>
@@ -1146,8 +1155,11 @@
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M4">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>100</v>
       </c>
@@ -1187,8 +1199,11 @@
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M5">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A6">
         <v>-100</v>
       </c>
@@ -1228,8 +1243,11 @@
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M6">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A7">
         <v>200</v>
       </c>
@@ -1269,8 +1287,11 @@
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M7">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A8">
         <v>-200</v>
       </c>
@@ -1310,8 +1331,11 @@
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M8">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A9">
         <v>0</v>
       </c>
@@ -1351,8 +1375,11 @@
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M9">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A10">
         <v>0</v>
       </c>
@@ -1392,8 +1419,11 @@
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M10">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A11">
         <v>310</v>
       </c>
@@ -1433,8 +1463,11 @@
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M11">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A12">
         <v>310</v>
       </c>
@@ -1474,8 +1507,11 @@
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M12">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A13">
         <v>310</v>
       </c>
@@ -1515,8 +1551,11 @@
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M13">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A14">
         <v>990</v>
       </c>
@@ -1556,8 +1595,11 @@
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M14">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A15">
         <v>990</v>
       </c>
@@ -1597,8 +1639,11 @@
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M15">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A16">
         <v>1555</v>
       </c>
@@ -1638,8 +1683,11 @@
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M16">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A17">
         <v>3480</v>
       </c>
@@ -1679,8 +1727,11 @@
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M17">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A18">
         <v>3480</v>
       </c>
@@ -1720,8 +1771,11 @@
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M18">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A19">
         <v>3480</v>
       </c>
@@ -1761,8 +1815,11 @@
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M19">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A20">
         <v>3480</v>
       </c>
@@ -1802,8 +1859,11 @@
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M20">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A21">
         <v>3480</v>
       </c>
@@ -1843,8 +1903,11 @@
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M21">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A22">
         <v>3680</v>
       </c>
@@ -1884,8 +1947,11 @@
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M22">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A23">
         <v>3680</v>
       </c>
@@ -1925,8 +1991,11 @@
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M23">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A24">
         <v>3280</v>
       </c>
@@ -1966,8 +2035,11 @@
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M24">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A25">
         <v>3280</v>
       </c>
@@ -2006,6 +2078,9 @@
       <c r="L25">
         <f t="shared" si="3"/>
         <v>20</v>
+      </c>
+      <c r="M25">
+        <v>-1</v>
       </c>
     </row>
   </sheetData>

--- a/Action/Data/CSV/MobEnemy1/MobEnemyData.xlsx
+++ b/Action/Data/CSV/MobEnemy1/MobEnemyData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ita20\OneDrive\デスクトップ\GameProject\Action\Data\CSV\MobEnemy1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6E1B49E1-DD48-4F8F-8F06-A3004FE0E07A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{78F62EBA-944C-4061-A302-F21EE186035E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1355,28 +1355,28 @@
         <v>0</v>
       </c>
       <c r="G9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J9">
         <f t="shared" si="1"/>
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="K9">
         <f t="shared" si="2"/>
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="L9">
         <f t="shared" si="3"/>
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.4">
@@ -1883,28 +1883,28 @@
         <v>0</v>
       </c>
       <c r="G21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J21">
         <f t="shared" si="1"/>
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="K21">
         <f t="shared" si="2"/>
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="L21">
         <f t="shared" si="3"/>
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.4">
@@ -1927,28 +1927,28 @@
         <v>0</v>
       </c>
       <c r="G22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J22">
         <f t="shared" si="1"/>
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="K22">
         <f t="shared" si="2"/>
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="L22">
         <f t="shared" si="3"/>
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.4">
@@ -1971,28 +1971,28 @@
         <v>0</v>
       </c>
       <c r="G23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J23">
         <f t="shared" si="1"/>
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="K23">
         <f t="shared" si="2"/>
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="L23">
         <f t="shared" si="3"/>
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.4">

--- a/Action/Data/CSV/MobEnemy1/MobEnemyData.xlsx
+++ b/Action/Data/CSV/MobEnemy1/MobEnemyData.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ita20\OneDrive\デスクトップ\GameProject\Action\Data\CSV\MobEnemy1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2409404\Desktop\GameProject\Action\Data\CSV\MobEnemy1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{78F62EBA-944C-4061-A302-F21EE186035E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{33F30372-854C-4725-AB40-0347043022D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -681,9 +681,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -721,7 +721,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -827,7 +827,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -969,7 +969,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1692,7 +1692,7 @@
         <v>3480</v>
       </c>
       <c r="B17">
-        <v>360</v>
+        <v>340</v>
       </c>
       <c r="C17">
         <v>-3230</v>
@@ -1736,7 +1736,7 @@
         <v>3480</v>
       </c>
       <c r="B18">
-        <v>360</v>
+        <v>340</v>
       </c>
       <c r="C18">
         <v>-3430</v>
@@ -1780,7 +1780,7 @@
         <v>3480</v>
       </c>
       <c r="B19">
-        <v>360</v>
+        <v>340</v>
       </c>
       <c r="C19">
         <v>-2830</v>
@@ -1824,7 +1824,7 @@
         <v>3480</v>
       </c>
       <c r="B20">
-        <v>360</v>
+        <v>340</v>
       </c>
       <c r="C20">
         <v>-2630</v>
@@ -1868,7 +1868,7 @@
         <v>3480</v>
       </c>
       <c r="B21">
-        <v>360</v>
+        <v>340</v>
       </c>
       <c r="C21">
         <v>-3030</v>
@@ -1912,7 +1912,7 @@
         <v>3680</v>
       </c>
       <c r="B22">
-        <v>360</v>
+        <v>340</v>
       </c>
       <c r="C22">
         <v>-3130</v>
@@ -1956,7 +1956,7 @@
         <v>3680</v>
       </c>
       <c r="B23">
-        <v>360</v>
+        <v>340</v>
       </c>
       <c r="C23">
         <v>-2930</v>
@@ -2000,7 +2000,7 @@
         <v>3280</v>
       </c>
       <c r="B24">
-        <v>360</v>
+        <v>340</v>
       </c>
       <c r="C24">
         <v>-3130</v>
@@ -2044,7 +2044,7 @@
         <v>3280</v>
       </c>
       <c r="B25">
-        <v>360</v>
+        <v>340</v>
       </c>
       <c r="C25">
         <v>-2930</v>

--- a/Action/Data/CSV/MobEnemy1/MobEnemyData.xlsx
+++ b/Action/Data/CSV/MobEnemy1/MobEnemyData.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2409404\Desktop\GameProject\Action\Data\CSV\MobEnemy1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ita20\OneDrive\デスクトップ\GameProject\Action\Data\CSV\MobEnemy1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{33F30372-854C-4725-AB40-0347043022D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EAFED6E4-975D-4994-9184-4473766163AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -681,9 +681,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 テーマ">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -721,7 +721,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -827,7 +827,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -969,7 +969,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -977,13 +977,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M25"/>
+  <dimension ref="A1:O25"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="16" width="5.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A1">
         <v>0</v>
       </c>
@@ -1026,8 +1026,14 @@
       <c r="M1">
         <v>-1</v>
       </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N1">
+        <v>5</v>
+      </c>
+      <c r="O1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>0</v>
       </c>
@@ -1070,8 +1076,14 @@
       <c r="M2">
         <v>-1</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N2">
+        <v>2</v>
+      </c>
+      <c r="O2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>50</v>
       </c>
@@ -1114,8 +1126,14 @@
       <c r="M3">
         <v>-1</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N3">
+        <v>5</v>
+      </c>
+      <c r="O3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>-50</v>
       </c>
@@ -1158,8 +1176,14 @@
       <c r="M4">
         <v>-1</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N4">
+        <v>5</v>
+      </c>
+      <c r="O4">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>100</v>
       </c>
@@ -1167,7 +1191,7 @@
         <v>100</v>
       </c>
       <c r="C5">
-        <v>-2260</v>
+        <v>-2360</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -1202,8 +1226,14 @@
       <c r="M5">
         <v>-1</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N5">
+        <v>2</v>
+      </c>
+      <c r="O5">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A6">
         <v>-100</v>
       </c>
@@ -1211,7 +1241,7 @@
         <v>100</v>
       </c>
       <c r="C6">
-        <v>-2260</v>
+        <v>-2360</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -1246,8 +1276,14 @@
       <c r="M6">
         <v>-1</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N6">
+        <v>2</v>
+      </c>
+      <c r="O6">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A7">
         <v>200</v>
       </c>
@@ -1290,8 +1326,14 @@
       <c r="M7">
         <v>-1</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N7">
+        <v>5</v>
+      </c>
+      <c r="O7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A8">
         <v>-200</v>
       </c>
@@ -1334,8 +1376,14 @@
       <c r="M8">
         <v>-1</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N8">
+        <v>5</v>
+      </c>
+      <c r="O8">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A9">
         <v>0</v>
       </c>
@@ -1378,8 +1426,14 @@
       <c r="M9">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N9">
+        <v>10</v>
+      </c>
+      <c r="O9">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A10">
         <v>0</v>
       </c>
@@ -1422,8 +1476,14 @@
       <c r="M10">
         <v>-1</v>
       </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N10">
+        <v>5</v>
+      </c>
+      <c r="O10">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A11">
         <v>310</v>
       </c>
@@ -1466,8 +1526,14 @@
       <c r="M11">
         <v>-1</v>
       </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N11">
+        <v>2</v>
+      </c>
+      <c r="O11">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A12">
         <v>310</v>
       </c>
@@ -1510,8 +1576,14 @@
       <c r="M12">
         <v>-1</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N12">
+        <v>2</v>
+      </c>
+      <c r="O12">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A13">
         <v>310</v>
       </c>
@@ -1554,8 +1626,14 @@
       <c r="M13">
         <v>-1</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N13">
+        <v>2</v>
+      </c>
+      <c r="O13">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A14">
         <v>990</v>
       </c>
@@ -1598,8 +1676,14 @@
       <c r="M14">
         <v>-1</v>
       </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N14">
+        <v>5</v>
+      </c>
+      <c r="O14">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A15">
         <v>990</v>
       </c>
@@ -1642,8 +1726,14 @@
       <c r="M15">
         <v>-1</v>
       </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N15">
+        <v>5</v>
+      </c>
+      <c r="O15">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A16">
         <v>1555</v>
       </c>
@@ -1686,8 +1776,14 @@
       <c r="M16">
         <v>-1</v>
       </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N16">
+        <v>2</v>
+      </c>
+      <c r="O16">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A17">
         <v>3480</v>
       </c>
@@ -1730,8 +1826,14 @@
       <c r="M17">
         <v>-1</v>
       </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N17">
+        <v>2</v>
+      </c>
+      <c r="O17">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A18">
         <v>3480</v>
       </c>
@@ -1774,8 +1876,14 @@
       <c r="M18">
         <v>-1</v>
       </c>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N18">
+        <v>5</v>
+      </c>
+      <c r="O18">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A19">
         <v>3480</v>
       </c>
@@ -1818,8 +1926,14 @@
       <c r="M19">
         <v>-1</v>
       </c>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N19">
+        <v>2</v>
+      </c>
+      <c r="O19">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A20">
         <v>3480</v>
       </c>
@@ -1862,8 +1976,14 @@
       <c r="M20">
         <v>-1</v>
       </c>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N20">
+        <v>5</v>
+      </c>
+      <c r="O20">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A21">
         <v>3480</v>
       </c>
@@ -1906,8 +2026,14 @@
       <c r="M21">
         <v>1</v>
       </c>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N21">
+        <v>10</v>
+      </c>
+      <c r="O21">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A22">
         <v>3680</v>
       </c>
@@ -1950,8 +2076,14 @@
       <c r="M22">
         <v>1</v>
       </c>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N22">
+        <v>5</v>
+      </c>
+      <c r="O22">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A23">
         <v>3680</v>
       </c>
@@ -1994,8 +2126,14 @@
       <c r="M23">
         <v>1</v>
       </c>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N23">
+        <v>5</v>
+      </c>
+      <c r="O23">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A24">
         <v>3280</v>
       </c>
@@ -2038,8 +2176,14 @@
       <c r="M24">
         <v>-1</v>
       </c>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N24">
+        <v>2</v>
+      </c>
+      <c r="O24">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A25">
         <v>3280</v>
       </c>
@@ -2081,6 +2225,12 @@
       </c>
       <c r="M25">
         <v>-1</v>
+      </c>
+      <c r="N25">
+        <v>2</v>
+      </c>
+      <c r="O25">
+        <v>50</v>
       </c>
     </row>
   </sheetData>
